--- a/StructureDefinition-inera-ehds-condition-functional.xlsx
+++ b/StructureDefinition-inera-ehds-condition-functional.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -673,7 +673,7 @@
     <t>Condition.clinicalStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.1}
 </t>
   </si>
   <si>
@@ -766,7 +766,7 @@
     <t>In this profile, Condition represents a health problem of the patient. Therefore one of the category value(s) must be problem-list-item.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/problem-type-uv-ips</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/problem-type-uv-ips|2.0.1</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -793,7 +793,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-severity|4.0.1</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -830,7 +830,7 @@
     <t>Code for a clinical problem (or absent/unknown problem) that is selected from SNOMED CT</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/problems-uv-ips</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/problems-uv-ips|2.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -872,7 +872,7 @@
     <t>Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1667,7 +1667,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="71.2578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="75.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1682,7 +1682,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.1875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-inera-ehds-condition-functional.xlsx
+++ b/StructureDefinition-inera-ehds-condition-functional.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-condition-functional.xlsx
+++ b/StructureDefinition-inera-ehds-condition-functional.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-condition-functional.xlsx
+++ b/StructureDefinition-inera-ehds-condition-functional.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -438,7 +438,7 @@
 </t>
   </si>
   <si>
-    <t>Källsystem HSA-id (functionalStatusAssessmentHeader.sourceSystemHSAId)</t>
+    <t>Källsystem HSA-id (functionalStatusAssessmentHeader.sourceSystemHSAId) – https://tjanstekatalogen.inera.se/Endpoint/{hsaId} (GENERAL-005)</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -673,7 +673,7 @@
     <t>Condition.clinicalStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.1}
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
 </t>
   </si>
   <si>
@@ -766,7 +766,7 @@
     <t>In this profile, Condition represents a health problem of the patient. Therefore one of the category value(s) must be problem-list-item.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/problem-type-uv-ips|2.0.1</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/problem-type-uv-ips</t>
   </si>
   <si>
     <t>&lt; 404684003 |Clinical finding|</t>
@@ -793,7 +793,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-severity|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -830,7 +830,7 @@
     <t>Code for a clinical problem (or absent/unknown problem) that is selected from SNOMED CT</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/problems-uv-ips|2.0.1</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/problems-uv-ips</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -872,7 +872,7 @@
     <t>Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1667,7 +1667,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="71.2578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1682,7 +1682,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.1875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
